--- a/combinations of first layer.xlsx
+++ b/combinations of first layer.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{46BDFACD-5FE9-8542-99D3-1F6FE179AD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC2FB0F-7572-444E-8E80-EE3ECA0A3D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36280" yWindow="-20620" windowWidth="28040" windowHeight="17440"/>
+    <workbookView xWindow="36420" yWindow="-20280" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combinations of first layer" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
   <si>
     <t>Pos</t>
   </si>
@@ -52,19 +52,22 @@
     <t>years</t>
   </si>
   <si>
-    <t>---- with - 3 - - - -   35510.977s       1,112,211,968 solutions</t>
+    <t>Without 6/9 alternates</t>
   </si>
   <si>
-    <t>Without 6/9 alternates</t>
+    <t>Pypy3.10 and available set logic</t>
+  </si>
+  <si>
+    <t>Based on result ---- with - 4 - - - -	5266.220s	 427,123,712 solutions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -202,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -385,6 +388,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,12 +559,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -911,8 +925,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
@@ -1038,9 +1052,7 @@
       <c r="D7" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -1071,156 +1083,344 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16">
         <v>0</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C16" s="1">
+        <f t="shared" ref="C16:C19" si="1">B16*C17</f>
+        <v>725760</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <f>C16/24</f>
+        <v>30240</v>
+      </c>
+      <c r="F16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <f>E16/365</f>
+        <v>82.849315068493155</v>
+      </c>
+      <c r="H16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" ref="C17:C20" si="1">B17*C18</f>
+        <f t="shared" si="1"/>
         <v>725760</v>
       </c>
       <c r="D17" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
-        <f>C17/24</f>
-        <v>30240</v>
-      </c>
-      <c r="F17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="2">
-        <f>E17/365</f>
-        <v>82.849315068493155</v>
-      </c>
-      <c r="H17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>725760</v>
+        <v>30240</v>
       </c>
       <c r="D18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>30240</v>
+        <v>1440</v>
       </c>
       <c r="D19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <f>B20*C21</f>
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>24</v>
+      </c>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="J24" s="6">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J25" s="6">
         <v>3</v>
       </c>
-      <c r="B20">
+      <c r="K25" s="6">
+        <v>4</v>
+      </c>
+      <c r="L25" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J26" s="6">
+        <v>6</v>
+      </c>
+      <c r="K26" s="6">
+        <v>7</v>
+      </c>
+      <c r="L26" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" ref="C30:C35" si="2">B30*C31</f>
+        <v>106162.56000000001</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <f>C30/24</f>
+        <v>4423.4400000000005</v>
+      </c>
+      <c r="F30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2">
+        <f>E30/365</f>
+        <v>12.119013698630138</v>
+      </c>
+      <c r="H30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
         <v>24</v>
       </c>
-      <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>1440</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="C31" s="1">
+        <f t="shared" si="2"/>
+        <v>106162.56000000001</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>21</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="2"/>
+        <v>4423.4400000000005</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>24</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="2"/>
+        <v>210.64000000000001</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>4</v>
       </c>
-      <c r="B21">
+      <c r="B34">
         <v>6</v>
       </c>
-      <c r="C21" s="1">
-        <f>B21*C22</f>
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="C34" s="1">
+        <f t="shared" si="2"/>
+        <v>8.7766666666666673</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>5</v>
       </c>
-      <c r="B22">
+      <c r="B35">
         <v>24</v>
       </c>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="C35" s="7">
+        <f>5266/3600</f>
+        <v>1.4627777777777777</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>6</v>
       </c>
-      <c r="B23">
+      <c r="B36">
         <v>21</v>
       </c>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>7</v>
       </c>
-      <c r="B24">
+      <c r="B37">
         <v>24</v>
       </c>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>8</v>
       </c>
-      <c r="B25">
+      <c r="B38">
         <v>21</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/combinations of first layer.xlsx
+++ b/combinations of first layer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC2FB0F-7572-444E-8E80-EE3ECA0A3D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52EC523-AF3F-3140-8991-1F301972B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36420" yWindow="-20280" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39620" yWindow="-19440" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combinations of first layer" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="13">
   <si>
     <t>Pos</t>
   </si>
@@ -58,7 +58,20 @@
     <t>Pypy3.10 and available set logic</t>
   </si>
   <si>
-    <t>Based on result ---- with - 4 - - - -	5266.220s	 427,123,712 solutions</t>
+    <t>--- with - 9 1 - - -	20061.588s	 1,507,742,720 solutions</t>
+  </si>
+  <si>
+    <t>--- with - 6 1 - - -	40029.570s	 3,015,485,440 solutions</t>
+  </si>
+  <si>
+    <t>Rust with bitset + inline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- with - 9 1 - - -     6398.358s 1,507,742,720 solutions
+</t>
+  </si>
+  <si>
+    <t>--- with - 6 1 - - -     12770.027s 3,015,485,440 solutions</t>
   </si>
 </sst>
 </file>
@@ -559,7 +572,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -569,7 +582,6 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -926,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
@@ -1294,22 +1306,22 @@
         <v>1</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" ref="C30:C35" si="2">B30*C31</f>
-        <v>106162.56000000001</v>
+        <f t="shared" ref="C30:C33" si="2">B30*C31</f>
+        <v>67199.999999999985</v>
       </c>
       <c r="D30" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="1">
         <f>C30/24</f>
-        <v>4423.4400000000005</v>
+        <v>2799.9999999999995</v>
       </c>
       <c r="F30" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="2">
         <f>E30/365</f>
-        <v>12.119013698630138</v>
+        <v>7.6712328767123275</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
@@ -1324,7 +1336,7 @@
       </c>
       <c r="C31" s="1">
         <f t="shared" si="2"/>
-        <v>106162.56000000001</v>
+        <v>67199.999999999985</v>
       </c>
       <c r="D31" t="s">
         <v>2</v>
@@ -1339,7 +1351,7 @@
       </c>
       <c r="C32" s="1">
         <f t="shared" si="2"/>
-        <v>4423.4400000000005</v>
+        <v>2799.9999999999995</v>
       </c>
       <c r="D32" t="s">
         <v>2</v>
@@ -1354,7 +1366,7 @@
       </c>
       <c r="C33" s="1">
         <f t="shared" si="2"/>
-        <v>210.64000000000001</v>
+        <v>133.33333333333331</v>
       </c>
       <c r="D33" t="s">
         <v>2</v>
@@ -1368,13 +1380,16 @@
         <v>6</v>
       </c>
       <c r="C34" s="1">
-        <f t="shared" si="2"/>
-        <v>8.7766666666666673</v>
+        <f>20000/3600</f>
+        <v>5.5555555555555554</v>
       </c>
       <c r="D34" t="s">
         <v>2</v>
       </c>
       <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
@@ -1383,16 +1398,13 @@
       <c r="B35">
         <v>24</v>
       </c>
-      <c r="C35" s="7">
-        <f>5266/3600</f>
-        <v>1.4627777777777777</v>
-      </c>
+      <c r="C35" s="5"/>
       <c r="D35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" t="s">
-        <v>8</v>
+      <c r="J35" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1421,6 +1433,158 @@
         <v>21</v>
       </c>
       <c r="C38" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" ref="C43:C46" si="3">B43*C44</f>
+        <v>21497.279999999999</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <f>C43/24</f>
+        <v>895.71999999999991</v>
+      </c>
+      <c r="F43" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="2">
+        <f>E43/365</f>
+        <v>2.4540273972602735</v>
+      </c>
+      <c r="H43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <v>24</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="3"/>
+        <v>21497.279999999999</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>2</v>
+      </c>
+      <c r="B45">
+        <v>21</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="3"/>
+        <v>895.72</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>24</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="3"/>
+        <v>42.653333333333336</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1">
+        <f>6398/3600</f>
+        <v>1.7772222222222223</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="J48" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>21</v>
+      </c>
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>7</v>
+      </c>
+      <c r="B50">
+        <v>24</v>
+      </c>
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="B51">
+        <v>21</v>
+      </c>
+      <c r="C51" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
